--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, HBase, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed75a25bf648004</t>
+          <t>https://www.indeed.com/viewjob?jk=706e3b72b66ba001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dynata</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Westport, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>28.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Dataflow, Spark</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c7347957879848</t>
+          <t>https://www.indeed.com/viewjob?jk=1a6fc35c45c62e0e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Cloud Infrastructure Engineer – AWS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RPA INFOTECH INDIA</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Photon, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c4bca427782367</t>
+          <t>https://www.indeed.com/viewjob?jk=616635db842b8721</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>21.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, HBase, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,89 +601,89 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0497d85a50331b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed75a25bf648004</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Dynata</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westport, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bcc00949b0b05a</t>
+          <t>https://www.indeed.com/viewjob?jk=66c7347957879848</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT Data Engineer IV</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SouthState Bank</t>
+          <t>RPA INFOTECH INDIA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Winter Haven, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Glue, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Photon, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c590723bea472d</t>
+          <t>https://www.indeed.com/viewjob?jk=77c4bca427782367</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
+          <t>https://www.indeed.com/viewjob?jk=9734810965d2b080</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956a4b8be14845b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0497d85a50331b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ac15a01e20fc4f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Back-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Medallion Architecture, Delta Live Tables, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230993df38e10727</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf29ed5270e11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BACK-END DEVELOPER — Investment Data Warehouse / GenBI, AI &amp; ML</t>
+          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Technology Digest inc</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>West Sacramento, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a478979da3d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Platform (DevOps) Engineer</t>
+          <t>IT Data Engineer IV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wise Skulls</t>
+          <t>SouthState Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Winter Haven, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
+          <t>https://www.indeed.com/viewjob?jk=89c590723bea472d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Production Operations Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a709e6e770f53ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineering Senior Advisor</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0531777dcadfb3</t>
+          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
+          <t>Software Engineering Senior Advisor</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
+          <t>https://www.indeed.com/viewjob?jk=4956a4b8be14845b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Platform Engineer VI Data Services</t>
+          <t>Front-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
+          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eurofins</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stafford, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
+          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Sr Analyst, Application Operations</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
+          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>BACK-END DEVELOPER — Investment Data Warehouse / GenBI, AI &amp; ML</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Technology Digest inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=21a478979da3d18d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Platform (DevOps) Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>Wise Skulls</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
+          <t>https://www.indeed.com/viewjob?jk=a709e6e770f53ae5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Rearc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0531777dcadfb3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
+          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Platform Engineer VI Data Services</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Eurofins</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stafford, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
+          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
+          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Medallion Architecture, Snowflake, Oracle, SQL Server, PostgreSQL, dbt, Power BI</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f9d967bd29018a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ICONICS</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
+          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d131fb25875c7944</t>
+          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e3d67c41aeb6bc</t>
+          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CDP Data Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8550b60dfa07a9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>ICONICS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,194 +1791,194 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
+          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cca7881ecab68e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d131fb25875c7944</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdcc2a4768c36ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e3d67c41aeb6bc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2a3affc587d7fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>CDP Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a67bb5e4a90ee02</t>
+          <t>https://www.indeed.com/viewjob?jk=8550b60dfa07a9a8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c03ba8ab959738</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1987,11 +1987,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
+          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer III</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, NoSQL, MLOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30414b2a85fbe095</t>
+          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
+          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Software Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
+          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, NoSQL, MLOps, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
+          <t>https://www.indeed.com/viewjob?jk=30414b2a85fbe095</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full-Stack SaaS Engineer</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Church Online, LLC</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b3c17f710c4b52</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Solutions Architect - Strategic High Tech</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Kafka, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd9053cc3b8b074</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2757,116 +2757,116 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>AI Architect (GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>StatusNeo Technology Consulting</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EXODUS INTEGRITY SERVICES (EIS)</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Broadview Heights, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a2bf4234ddf040</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Full-Stack SaaS Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>The Church Online, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
+          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defd80f2620eb381</t>
+          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Programmer-Developer II/Sr.</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92658d4e06ae2705</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=96b3c17f710c4b52</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Network Automation Engineer</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (contract)</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Solutions Architect - Strategic High Tech</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Kafka, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,19 +3331,19 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd9053cc3b8b074</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3352,81 +3352,81 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d356d9379a1d876</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Programmer-Developer II/Sr.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
+          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,822 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DevSecOps / Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>OpenShift Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Data Engineer - Compensation Systems</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Sunbelt Rentals</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Sunbelt Rentals</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NetImpact Strategies Inc</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8054e0d11a96c035</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>PLM Technical Consultant</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9108179d508b8714</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Python Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Full Stack Solutions Developer – Java</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Full Stack Solutions Developer – Java</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Kafka Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Java Application Architect</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AWS Cloud Architect (contract)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Microsoft Azure Specialist</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d356d9379a1d876</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Network Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Equinix</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Texas City, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>UT Health Science Center at San Antonio</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Rearc</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>Systems Engineer SME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>23.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, ECS, IAM</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616635db842b8721</t>
+          <t>https://www.indeed.com/viewjob?jk=73e738969e8679aa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Cloud Infrastructure Engineer – AWS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, HBase, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed75a25bf648004</t>
+          <t>https://www.indeed.com/viewjob?jk=616635db842b8721</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dynata</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Westport, CT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Dataflow, Spark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, HBase, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c7347957879848</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed75a25bf648004</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RPA INFOTECH INDIA</t>
+          <t>Dynata</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Westport, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Photon, GCP</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c4bca427782367</t>
+          <t>https://www.indeed.com/viewjob?jk=66c7347957879848</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>RPA INFOTECH INDIA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Photon, GCP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9734810965d2b080</t>
+          <t>https://www.indeed.com/viewjob?jk=77c4bca427782367</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0497d85a50331b</t>
+          <t>https://www.indeed.com/viewjob?jk=9734810965d2b080</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ac15a01e20fc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0497d85a50331b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Back-End/Full-Stack Developer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf29ed5270e11</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ac15a01e20fc4f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
+          <t>Back-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf29ed5270e11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT Data Engineer IV</t>
+          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SouthState Bank</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Winter Haven, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c590723bea472d</t>
+          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Production Operations Engineer</t>
+          <t>IT Data Engineer IV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>SouthState Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Winter Haven, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
+          <t>https://www.indeed.com/viewjob?jk=89c590723bea472d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor</t>
+          <t>Senior Production Operations Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
+          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor</t>
+          <t>Senior Production Operations Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956a4b8be14845b</t>
+          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Front-End/Full-Stack Developer</t>
+          <t>Software Engineering Senior Advisor</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineering Senior Advisor</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=4956a4b8be14845b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Analyst, Application Operations</t>
+          <t>Front-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
+          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BACK-END DEVELOPER — Investment Data Warehouse / GenBI, AI &amp; ML</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Technology Digest inc</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>West Sacramento, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a478979da3d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Platform (DevOps) Engineer</t>
+          <t>Sr Analyst, Application Operations</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wise Skulls</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
+          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BACK-END DEVELOPER — Investment Data Warehouse / GenBI, AI &amp; ML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Technology Digest inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>West Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a709e6e770f53ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=21a478979da3d18d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform (DevOps) Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>Wise Skulls</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0531777dcadfb3</t>
+          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=a709e6e770f53ae5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Rearc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0531777dcadfb3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Platform Engineer VI Data Services</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
+          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Eurofins</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Stafford, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Platform Engineer VI Data Services</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
+          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Eurofins</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Stafford, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
+          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
+          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ICONICS</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
+          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d131fb25875c7944</t>
+          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Cybersecurity Sr Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e3d67c41aeb6bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ICONICS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
+          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CDP Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8550b60dfa07a9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e3d67c41aeb6bc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>CDP Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=8550b60dfa07a9a8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
+          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer III</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, NoSQL, MLOps, Docker</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30414b2a85fbe095</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
@@ -2468,12 +2468,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
+          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Software Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
+          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, NoSQL, MLOps, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
+          <t>https://www.indeed.com/viewjob?jk=30414b2a85fbe095</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Architect (GenAI &amp; Agentic AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>StatusNeo Technology Consulting</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
+          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full-Stack SaaS Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Church Online, LLC</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Full-Stack SaaS Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>The Church Online, LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Architect (GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>StatusNeo Technology Consulting</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b3c17f710c4b52</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solutions Architect - Strategic High Tech</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd9053cc3b8b074</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=96b3c17f710c4b52</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Programmer-Developer II/Sr.</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Architect - Strategic High Tech</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Kafka, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,102 +3611,102 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd9053cc3b8b074</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NetImpact Strategies Inc</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8054e0d11a96c035</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PLM Technical Consultant</t>
+          <t>Programmer-Developer II/Sr.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9108179d508b8714</t>
+          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Python Solutions Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Python Solutions Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d356d9379a1d876</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Network Automation Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+          <t>Developer - Information Technology</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e9e55514658931</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>NetImpact Strategies Inc</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, SQS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+          <t>https://www.indeed.com/viewjob?jk=8054e0d11a96c035</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,19 +4416,19 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Microsoft Azure Specialist</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4441,17 +4441,367 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d356d9379a1d876</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Texas City, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Rearc</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
           <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Network Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Equinix</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>UT Health Science Center at San Antonio</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>BRMi</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,25 +1343,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
+          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer VI Data Services</t>
+          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer VI Data Services</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Eurofins</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stafford, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
+          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Eurofins</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Stafford, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,69 +1466,69 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
+          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
+          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
+          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
+          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cybersecurity Sr Engineer</t>
+          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
+          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cybersecurity Sr Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ICONICS</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e3d67c41aeb6bc</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ICONICS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,59 +1966,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
+          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CDP Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8550b60dfa07a9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e3d67c41aeb6bc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>CDP Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=8550b60dfa07a9a8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
+          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
+          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
+          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer III</t>
+          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,15 +2508,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
+          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, NoSQL, MLOps, Docker</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30414b2a85fbe095</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Software Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, NoSQL, MLOps, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=30414b2a85fbe095</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
+          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
+          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-Stack SaaS Engineer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Church Online, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Architect (GenAI &amp; Agentic AI)</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>StatusNeo Technology Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Full-Stack SaaS Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>The Church Online, LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>AI Architect (GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>StatusNeo Technology Consulting</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,42 +3251,42 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
+          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b3c17f710c4b52</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Solutions Architect - Strategic High Tech</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Kafka, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,19 +3611,19 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd9053cc3b8b074</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Architect - Strategic High Tech</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Kafka, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd9053cc3b8b074</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Programmer-Developer II/Sr.</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
+          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Programmer-Developer II/Sr.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,14 +4066,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Python Solutions Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Developer - Information Technology</t>
+          <t>Python Solutions Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
+          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DATA SCIENTIST</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e9e55514658931</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NetImpact Strategies Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8054e0d11a96c035</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+          <t>Developer - Information Technology</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e9e55514658931</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior Network Automation Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,14 +4556,14 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
+          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
+          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Network Automation Engineer</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
+          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>Rearc</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,15 +4791,85 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>UT Health Science Center at San Antonio</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>BRMi</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dynata</t>
+          <t>RPA INFOTECH INDIA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Westport, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Dataflow, Spark</t>
+          <t>AWS, Glue, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Photon, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c7347957879848</t>
+          <t>https://www.indeed.com/viewjob?jk=77c4bca427782367</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RPA INFOTECH INDIA</t>
+          <t>Dynata</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Westport, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Photon, GCP</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c4bca427782367</t>
+          <t>https://www.indeed.com/viewjob?jk=66c7347957879848</t>
         </is>
       </c>
     </row>
@@ -888,35 +888,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IT Data Engineer IV</t>
+          <t>Senior Production Operations Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SouthState Bank</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Winter Haven, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c590723bea472d</t>
+          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
         </is>
       </c>
     </row>
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Production Operations Engineer</t>
+          <t>Software Engineering Senior Advisor</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
+          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
         </is>
       </c>
     </row>
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
+          <t>https://www.indeed.com/viewjob?jk=4956a4b8be14845b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor</t>
+          <t>Front-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956a4b8be14845b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Front-End/Full-Stack Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr Analyst, Application Operations</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Analyst, Application Operations</t>
+          <t>BACK-END DEVELOPER — Investment Data Warehouse / GenBI, AI &amp; ML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Technology Digest inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>West Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
+          <t>https://www.indeed.com/viewjob?jk=21a478979da3d18d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BACK-END DEVELOPER — Investment Data Warehouse / GenBI, AI &amp; ML</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Technology Digest inc</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>West Sacramento, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a478979da3d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform (DevOps) Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wise Skulls</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
+          <t>https://www.indeed.com/viewjob?jk=a709e6e770f53ae5</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Rearc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a709e6e770f53ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0531777dcadfb3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0531777dcadfb3</t>
+          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Platform (DevOps) Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Wise Skulls</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Platform Engineer VI Data Services</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
+          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
+          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Platform Engineer VI Data Services</t>
+          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
         </is>
       </c>
     </row>
@@ -1483,52 +1483,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Cybersecurity Sr Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>ICONICS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
+          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
+          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
+          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cybersecurity Sr Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ICONICS</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,69 +1956,69 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e3d67c41aeb6bc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e3d67c41aeb6bc</t>
+          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CDP Data Engineer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8550b60dfa07a9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>CDP Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=8550b60dfa07a9a8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,19 +2176,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
+          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer III</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, NoSQL, MLOps, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30414b2a85fbe095</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Full-Stack SaaS Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>The Church Online, LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Architect (GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>StatusNeo Technology Consulting</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
+          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
@@ -2958,12 +2958,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
+          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full-Stack SaaS Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Church Online, LLC</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI Architect (GenAI &amp; Agentic AI)</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>StatusNeo Technology Consulting</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,29 +3251,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
+          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect - Strategic High Tech</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Kafka, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,19 +3611,19 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd9053cc3b8b074</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Solutions Architect - Strategic High Tech</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Kafka, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd9053cc3b8b074</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
+          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>Programmer-Developer II/Sr.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Programmer-Developer II/Sr.</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,14 +4066,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Python Solutions Engineer</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,14 +4276,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Python Solutions Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Developer - Information Technology</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (contract)</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e9e55514658931</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d356d9379a1d876</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Developer - Information Technology</t>
+          <t>Senior Network Automation Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DATA SCIENTIST</t>
+          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e9e55514658931</t>
+          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Network Automation Engineer</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,14 +4556,14 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
+          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Rearc</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
+          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4800,76 +4800,6 @@
         </is>
       </c>
       <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RPA INFOTECH INDIA</t>
+          <t>Dynata</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Westport, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Photon, GCP</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c4bca427782367</t>
+          <t>https://www.indeed.com/viewjob?jk=66c7347957879848</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dynata</t>
+          <t>RPA INFOTECH INDIA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Westport, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Dataflow, Spark</t>
+          <t>AWS, Glue, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Photon, GCP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c7347957879848</t>
+          <t>https://www.indeed.com/viewjob?jk=77c4bca427782367</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Platform (DevOps) Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Wise Skulls</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
+          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Platform (DevOps) Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wise Skulls</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
+          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Platform Engineer VI Data Services</t>
+          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Platform Engineer VI Data Services</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
+          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Eurofins</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stafford, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
+          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eurofins</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Stafford, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
+          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cybersecurity Sr Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
+          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ICONICS</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
+          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Cybersecurity Sr Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>ICONICS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
+          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CDP Data Engineer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8550b60dfa07a9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
+          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
+          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
+          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
+          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,19 +2631,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full-Stack SaaS Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Church Online, LLC</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Architect (GenAI &amp; Agentic AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>StatusNeo Technology Consulting</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
+          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack SaaS Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>The Church Online, LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
+          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Architect (GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>StatusNeo Technology Consulting</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
+          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Solutions Architect - Strategic High Tech</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Kafka, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd9053cc3b8b074</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Solutions Architect - Strategic High Tech</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Kafka, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,19 +3786,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd9053cc3b8b074</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Programmer-Developer II/Sr.</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Programmer-Developer II/Sr.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,67 +3961,67 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,19 +4031,19 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4052,11 +4052,11 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (contract)</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Python Solutions Engineer</t>
+          <t>Developer - Information Technology</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Developer - Information Technology</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e9e55514658931</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DATA SCIENTIST</t>
+          <t>AI WebCoder</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e9e55514658931</t>
+          <t>https://www.indeed.com/viewjob?jk=b74d9bc113520762</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Network Automation Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Python Solutions Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior Network Automation Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
+          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,15 +4791,190 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Rearc</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BRMi</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Solutions Architect - Strategic High Tech</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Kafka, ELT</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd9053cc3b8b074</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Programmer-Developer II/Sr.</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
+          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Programmer-Developer II/Sr.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
+          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,14 +4206,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer - Information Technology</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Developer - Information Technology</t>
+          <t>AI WebCoder</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
+          <t>https://www.indeed.com/viewjob?jk=b74d9bc113520762</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DATA SCIENTIST</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,19 +4346,19 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e9e55514658931</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI WebCoder</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4371,24 +4371,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74d9bc113520762</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,14 +4416,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (contract)</t>
+          <t>Python Solutions Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Network Automation Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Python Solutions Engineer</t>
+          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
+          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Network Automation Engineer</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
+          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Rearc</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4905,76 +4905,6 @@
         </is>
       </c>
       <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Rearc</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Cybersecurity Sr Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cybersecurity Sr Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-Stack SaaS Engineer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Church Online, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Architect (GenAI &amp; Agentic AI)</t>
+          <t>Full-Stack SaaS Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>StatusNeo Technology Consulting</t>
+          <t>The Church Online, LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
+          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>AI Architect (GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>StatusNeo Technology Consulting</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
         </is>
       </c>
     </row>
@@ -4108,17 +4108,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,14 +4206,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Developer - Information Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,19 +4276,19 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI WebCoder</t>
+          <t>Python Solutions Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4301,24 +4301,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74d9bc113520762</t>
+          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4381,14 +4381,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,14 +4416,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
@@ -4528,17 +4528,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Python Solutions Engineer</t>
+          <t>Developer - Information Technology</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
         </is>
       </c>
     </row>
@@ -4808,17 +4808,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Rearc</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cybersecurity Sr Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Cybersecurity Sr Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Python Solutions Engineer</t>
+          <t>Developer - Information Technology</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Python Solutions Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
         </is>
       </c>
     </row>
@@ -4381,14 +4381,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,14 +4416,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (contract)</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Developer - Information Technology</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
+          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Cybersecurity Sr Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cybersecurity Sr Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
@@ -1938,52 +1938,52 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e3d67c41aeb6bc</t>
+          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,19 +2141,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
+          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
+          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
+          <t>Software Engineer III - Full Stack</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
+          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>ISSM / Security Automation Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,19 +3751,19 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
+          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Programmer-Developer II/Sr.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Programmer-Developer II/Sr.</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
+          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,14 +4241,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Developer - Information Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Spark, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c32bb2b80f4dc7f9</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Python Solutions Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
@@ -4416,14 +4416,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (contract)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Network Automation Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Network Automation Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Rearc</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
+          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
+          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4870,41 +4870,6 @@
         </is>
       </c>
       <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
+          <t>Software Engineering - Senior Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Production Operations Engineer</t>
+          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
         </is>
       </c>
     </row>
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
+          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor</t>
+          <t>Senior Production Operations Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
+          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
         </is>
       </c>
     </row>
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956a4b8be14845b</t>
+          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Front-End/Full-Stack Developer</t>
+          <t>Software Engineering Senior Advisor</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=4956a4b8be14845b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Front-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Analyst, Application Operations</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
+          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BACK-END DEVELOPER — Investment Data Warehouse / GenBI, AI &amp; ML</t>
+          <t>Sr Analyst, Application Operations</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Technology Digest inc</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>West Sacramento, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a478979da3d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform (DevOps) Engineer</t>
+          <t>BACK-END DEVELOPER — Investment Data Warehouse / GenBI, AI &amp; ML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wise Skulls</t>
+          <t>Technology Digest inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
+          <t>https://www.indeed.com/viewjob?jk=21a478979da3d18d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform (DevOps) Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Wise Skulls</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a709e6e770f53ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0531777dcadfb3</t>
+          <t>https://www.indeed.com/viewjob?jk=a709e6e770f53ae5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Rearc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0531777dcadfb3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
+          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
+          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer VI Data Services</t>
+          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer VI Data Services</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Eurofins</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stafford, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
+          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Eurofins</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Stafford, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,69 +1466,69 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
+          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
+          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
+          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
+          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cybersecurity Sr Engineer</t>
+          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
+          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cybersecurity Sr Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ICONICS</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ICONICS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
+          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,19 +2141,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
+          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
+          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack</t>
+          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,69 +2481,69 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
+          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Software Engineer III - Full Stack</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
+          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
+          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Cloud Software Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
+          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
+          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
+          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,19 +3261,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,77 +3296,77 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
+          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
+          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3396,29 +3396,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
+          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ISSM / Security Automation Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,19 +3751,19 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>ISSM / Security Automation Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,19 +3786,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Programmer-Developer II/Sr.</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
+          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,59 +4101,59 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>Programmer-Developer II/Sr.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,14 +4381,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,14 +4416,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (contract)</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Network Automation Engineer</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
+          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>Rearc</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,15 +4861,50 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BRMi</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
+          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,42 +3366,42 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
+          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
+          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
+          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
         </is>
       </c>
     </row>
@@ -3466,29 +3466,29 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
+          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ISSM / Security Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,19 +3786,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>ISSM / Security Automation Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,19 +3856,19 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Programmer-Developer II/Sr.</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,67 +4171,67 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Programmer-Developer II/Sr.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,14 +4381,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,14 +4486,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (contract)</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
+          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
+          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,15 +4896,120 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>UT Health Science Center at San Antonio</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Rearc</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>BRMi</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0531777dcadfb3</t>
+          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
+          <t>Platform Engineer VI Data Services</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
+          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Platform Engineer VI Data Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Eurofins</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stafford, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
+          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eurofins</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Stafford, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,69 +1466,69 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
+          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
+          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
+          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
+          <t>Cybersecurity Sr Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>ICONICS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cybersecurity Sr Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
+          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ICONICS</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,19 +1966,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
+          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
+          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
+          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
+          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
+          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Software Engineer III - Full Stack</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,59 +2491,59 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
+          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Cloud Software Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
+          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
+          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Full-Stack SaaS Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Church Online, LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full-Stack SaaS Engineer</t>
+          <t>AI Architect (GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The Church Online, LLC</t>
+          <t>StatusNeo Technology Consulting</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Architect (GenAI &amp; Agentic AI)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>StatusNeo Technology Consulting</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Programmer-Developer II/Sr.</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, ETL, Jenkins, Docker, Kubernetes, Jenkins, Bitbucket, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507b26229191c569</t>
+          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,14 +4451,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,24 +4546,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (contract)</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,14 +4731,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
+          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
+          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1448,52 +1448,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa113d93b209abba</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
+          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
+          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Cybersecurity Sr Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cybersecurity Sr Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>ICONICS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
+          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ICONICS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
+          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Software Engineer III - Full Stack</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Kafka, Snowflake, PostgreSQL, MLOps, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,59 +2421,59 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
+          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Cloud Software Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>NOVOGRADAC &amp; COMPANY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
+          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
+          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,19 +2981,19 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Full-Stack SaaS Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Church Online, LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-Stack SaaS Engineer</t>
+          <t>AI Architect (GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Church Online, LLC</t>
+          <t>StatusNeo Technology Consulting</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Architect (GenAI &amp; Agentic AI)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>StatusNeo Technology Consulting</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
+          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,77 +3331,77 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
+          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3431,29 +3431,29 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>ISSM / Security Automation Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,19 +3786,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ISSM / Security Automation Engineer</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,19 +3821,19 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,24 +4546,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (contract)</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,14 +4731,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
+          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4905,111 +4905,6 @@
         </is>
       </c>
       <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1448,12 +1448,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
+          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
+          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ICONICS</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ICONICS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
+          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
+          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
+          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,59 +2421,59 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Full Stack</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer III</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Software Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9760fadd58dc6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ff5ec36207cba7</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f0ae852975856</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NOVOGRADAC &amp; COMPANY</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1352988239f97b32</t>
+          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
+          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,102 +3226,102 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ISSM / Security Automation Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,29 +3741,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>ISSM / Security Automation Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,19 +3821,19 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
@@ -4043,20 +4043,20 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,67 +4066,67 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,24 +4301,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (contract)</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
+          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4765,146 +4765,6 @@
         </is>
       </c>
       <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Front-End/Full-Stack Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Front-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Analyst, Application Operations</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
+          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BACK-END DEVELOPER — Investment Data Warehouse / GenBI, AI &amp; ML</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Technology Digest inc</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>West Sacramento, CA, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a478979da3d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform (DevOps) Engineer</t>
+          <t>Sr Analyst, Application Operations</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wise Skulls</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
+          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BACK-END DEVELOPER — Investment Data Warehouse / GenBI, AI &amp; ML</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Technology Digest inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>West Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a709e6e770f53ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=21a478979da3d18d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Platform (DevOps) Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Wise Skulls</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
+          <t>https://www.indeed.com/viewjob?jk=a709e6e770f53ae5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
+          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer VI Data Services</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
+          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Eurofins</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stafford, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Platform Engineer VI Data Services</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Eurofins</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Stafford, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
+          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Itron</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>ICONICS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
+          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, Spark, Scala, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cybersecurity Sr Engineer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, SQL Server, MySQL, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ICONICS</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355fbee9537a593d</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Engineer III - Full Stack</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
+          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Cloud Software Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,59 +2421,59 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer III</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Full-Stack SaaS Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>The Church Online, LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Snowflake, Data Modeling, dbt</t>
+          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
+          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Architect (GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>StatusNeo Technology Consulting</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,137 +2981,137 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full-Stack SaaS Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Church Online, LLC</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Architect (GenAI &amp; Agentic AI)</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>StatusNeo Technology Consulting</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52a161d21263c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
+          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>ISSM / Security Automation Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ISSM / Security Automation Engineer</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,124 +3821,124 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3947,11 +3947,11 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>SHAKTECH CORP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
+          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (contract)</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4520,251 +4520,6 @@
         </is>
       </c>
       <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e73c10ae052d85b</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a709e6e770f53ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
+          <t>Platform Engineer VI Data Services</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
+          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Platform Engineer VI Data Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Eurofins</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stafford, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,54 +1476,54 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
+          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eurofins</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Stafford, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Itron</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Itron</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>ICONICS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,42 +1721,42 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ICONICS</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Software Engineer III - Full Stack</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,69 +2236,69 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Software Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
+          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer III</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full-Stack SaaS Engineer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Church Online, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Data Modeling, ETL, dbt, Power BI, Tableau, CI/CD, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,112 +2866,112 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ISSM / Security Automation Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,29 +3391,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>ISSM / Security Automation Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,19 +3471,19 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,77 +3636,77 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Frontapp</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SHAKTECH CORP</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SHAKTECH CORP</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4170,356 +4170,6 @@
         </is>
       </c>
       <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>AWS Cloud Architect (contract)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Hilton</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - TX - Mandarin Speaking</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Texas City, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=948a17ca173019b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c64359435c0e75f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7085011cb79be32e</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=618b210528315c81</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a89c508623950b60</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb962ca1a1ab408</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Dynata</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Westport, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, HBase, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed75a25bf648004</t>
+          <t>https://www.indeed.com/viewjob?jk=66c7347957879848</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dynata</t>
+          <t>RPA INFOTECH INDIA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Westport, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Dataflow, Spark</t>
+          <t>AWS, Glue, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Photon, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c7347957879848</t>
+          <t>https://www.indeed.com/viewjob?jk=77c4bca427782367</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RPA INFOTECH INDIA</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Photon, GCP</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c4bca427782367</t>
+          <t>https://www.indeed.com/viewjob?jk=9734810965d2b080</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9734810965d2b080</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0497d85a50331b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0497d85a50331b</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ac15a01e20fc4f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Back-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ac15a01e20fc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf29ed5270e11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Back-End/Full-Stack Developer</t>
+          <t>Software Engineering - Senior Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf29ed5270e11</t>
+          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineering - Senior Engineer</t>
+          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
+          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
+          <t>Senior Production Operations Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
+          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
         </is>
       </c>
     </row>
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Production Operations Engineer</t>
+          <t>Software Engineering Senior Advisor</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
+          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor</t>
+          <t>Front-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956a4b8be14845b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
+          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Front-End/Full-Stack Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr Analyst, Application Operations</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>BACK-END DEVELOPER — Investment Data Warehouse / GenBI, AI &amp; ML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Technology Digest inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>West Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
+          <t>https://www.indeed.com/viewjob?jk=21a478979da3d18d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Analyst, Application Operations</t>
+          <t>Platform (DevOps) Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Wise Skulls</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
+          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BACK-END DEVELOPER — Investment Data Warehouse / GenBI, AI &amp; ML</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Technology Digest inc</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>West Sacramento, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a478979da3d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Platform (DevOps) Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wise Skulls</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
+          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Platform Engineer VI Data Services</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
+          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Eurofins</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stafford, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
+          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Platform Engineer VI Data Services</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eurofins</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Stafford, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Itron</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,102 +1581,102 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Itron</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ICONICS</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
+          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Software Engineer III - Full Stack</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
+          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Cloud Software Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,54 +2176,54 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2232,38 +2232,38 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer III</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>AI Architect (GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>StatusNeo Technology Consulting</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,102 +2736,102 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Architect (GenAI &amp; Agentic AI)</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>StatusNeo Technology Consulting</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
+          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>ISSM / Security Automation Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ISSM / Security Automation Engineer</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>PLSQL Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>i3 Consulting</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,102 +3506,102 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,19 +3716,19 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Frontapp</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>SHAKTECH CORP</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Frontapp</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SHAKTECH CORP</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,24 +3951,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>AWS Cloud Architect (contract)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4065,111 +4065,6 @@
         </is>
       </c>
       <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>AWS Cloud Architect (contract)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Hilton</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,60 +538,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Systems Engineer SME</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.6</v>
+        <v>25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e738969e8679aa</t>
+          <t>https://www.indeed.com/viewjob?jk=5d356376aee9aed9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>Systems Engineer SME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.2</v>
+        <v>23.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, ECS, IAM</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616635db842b8721</t>
+          <t>https://www.indeed.com/viewjob?jk=73e738969e8679aa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Infrastructure Engineer – AWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dynata</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Westport, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Dataflow, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c7347957879848</t>
+          <t>https://www.indeed.com/viewjob?jk=616635db842b8721</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RPA INFOTECH INDIA</t>
+          <t>Dynata</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Westport, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Photon, GCP</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c4bca427782367</t>
+          <t>https://www.indeed.com/viewjob?jk=66c7347957879848</t>
         </is>
       </c>
     </row>
@@ -1168,25 +1168,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BACK-END DEVELOPER — Investment Data Warehouse / GenBI, AI &amp; ML</t>
+          <t>Platform (DevOps) Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Technology Digest inc</t>
+          <t>Wise Skulls</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>West Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a478979da3d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform (DevOps) Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wise Skulls</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
+          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Eurofins</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stafford, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
+          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Platform Engineer VI Data Services</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Eurofins</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Stafford, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Itron</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Itron</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
@@ -2043,52 +2043,52 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer III</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Kafka, MySQL, MongoDB</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac607ddc0e1cc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Snowflake, Oracle, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff372041e842459</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>AI Architect (GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>StatusNeo Technology Consulting</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Architect (GenAI &amp; Agentic AI)</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>StatusNeo Technology Consulting</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,112 +2621,112 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>ISSM / Security Automation Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ISSM / Security Automation Engineer</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,42 +3321,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,102 +3366,102 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Azure, GCP, Vertex AI, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e00a75e4a5ed271</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c28f56c13c2e0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PLSQL Developer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>i3 Consulting</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2f584cd142ee68</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Application Development Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Scala, Kafka, Oracle, Jenkins, Maven, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=4000419aead97d7c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Senior Software Developer Engineer in Testing</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=d369a229cb2f75b9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Frontapp</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>SHAKTECH CORP</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Frontapp</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SHAKTECH CORP</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
+          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,24 +3846,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,122 +3951,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>AWS Cloud Architect (contract)</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Hilton</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, Scala, DynamoDB, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=351b70d13dc3de68</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
+          <t>https://www.indeed.com/viewjob?jk=f732389fad9f5f1e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform (DevOps) Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wise Skulls</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a014a83c45a16edc</t>
+          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,89 +1266,89 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
+          <t>Data Engineer Job</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
+          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Eurofins</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stafford, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>Itron</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Itron</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,69 +1466,69 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data Engineer, Berxi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,59 +1791,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, MongoDB, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Snowflake, Oracle, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff372041e842459</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, SQL Server, DynamoDB, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
+          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,112 +2376,112 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Snowflake, Oracle, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff372041e842459</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Architect (GenAI &amp; Agentic AI)</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>StatusNeo Technology Consulting</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
+          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
+          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>ISSM / Security Automation Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, ELT, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce4e28923d1134c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ISSM / Security Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,94 +3261,94 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Developer Engineer in Testing</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d369a229cb2f75b9</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Application Development Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, Scala, Kafka, Oracle, Jenkins, Maven, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=4000419aead97d7c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Frontapp</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
+          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>SHAKTECH CORP</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
+          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Application Development Senior Advisor- Hybrid</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, Jenkins, Maven, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4000419aead97d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Developer Engineer in Testing</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Kafka</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d369a229cb2f75b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Frontapp</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=f732389fad9f5f1e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SHAKTECH CORP</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,262 +3706,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
+          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Luxoft</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Kafka Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=332255b8348a2d43</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Java Application Architect</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, CI/CD, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f732389fad9f5f1e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dynata</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Westport, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Dataflow, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c7347957879848</t>
+          <t>https://www.indeed.com/viewjob?jk=9734810965d2b080</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9734810965d2b080</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0497d85a50331b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0497d85a50331b</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ac15a01e20fc4f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Back-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ac15a01e20fc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf29ed5270e11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Back-End/Full-Stack Developer</t>
+          <t>Software Engineering - Senior Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf29ed5270e11</t>
+          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineering - Senior Engineer</t>
+          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
+          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
+          <t>Senior Production Operations Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
+          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
         </is>
       </c>
     </row>
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Production Operations Engineer</t>
+          <t>Software Engineering Senior Advisor</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
+          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Front-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
+          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Front-End/Full-Stack Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Analyst, Application Operations</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
+          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Analyst, Application Operations</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
+          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,94 +1196,94 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer Job</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
+          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Cloud Storage, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer Job</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>Itron</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,112 +1326,112 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Kafka, ELT, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer, Berxi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AI Fire</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Itron</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Senior Engineer, Database Administration</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>Guardian Life</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Bethlehem, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Berxi</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,77 +1571,77 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Konnect Admin/Billing</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,172 +1791,172 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,59 +1966,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Snowflake, Oracle, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff372041e842459</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Snowflake, Oracle, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff372041e842459</t>
+          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,102 +2281,102 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ISSM / Security Automation Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2160f0a5605e5661</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,112 +2726,112 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31b9600d6bd6bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ISSM / Security Automation Engineer</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2862,11 +2862,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec1d8f9a0d3b90a</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Software Developer Engineer in Testing</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=d369a229cb2f75b9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SHAKTECH CORP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Application Development Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Scala, Kafka, Oracle, Jenkins, Maven, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=4000419aead97d7c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Frontapp</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce4e28923d1134c</t>
+          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=f732389fad9f5f1e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3295,426 +3295,6 @@
         </is>
       </c>
       <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Data Engineer - Compensation Systems</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Sunbelt Rentals</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e642074188f57324</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Sunbelt Rentals</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb33b3895c19f447</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Software Developer Engineer in Testing</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>The Clearing House Payments Company</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Kafka</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d369a229cb2f75b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Application Development Senior Advisor- Hybrid</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>The Cigna Group</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Bloomfield, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Scala, Kafka, Oracle, Jenkins, Maven, Jenkins, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4000419aead97d7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Frontapp</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Database Architect</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>SHAKTECH CORP</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Woodlawn, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Luxoft</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, CI/CD, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f732389fad9f5f1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
         </is>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer — AI/ML Data Platforms</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>T. Mims Corp.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0497d85a50331b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac713d0689b63faa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ac15a01e20fc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0497d85a50331b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Back-End/Full-Stack Developer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf29ed5270e11</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ac15a01e20fc4f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineering - Senior Engineer</t>
+          <t>Back-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf29ed5270e11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
+          <t>Software Engineering - Senior Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Production Operations Engineer</t>
+          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
         </is>
       </c>
     </row>
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
+          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor</t>
+          <t>Senior Production Operations Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
+          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineering Senior Advisor</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
+          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Front-End/Full-Stack Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Front-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d24b9231ae36f2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
         </is>
       </c>
     </row>
@@ -1098,35 +1098,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Analyst, Application Operations</t>
+          <t>Snowflake_DBT Developers</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=703f9ee27f04ed89</t>
+          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
         </is>
       </c>
     </row>
@@ -1203,25 +1203,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer Job</t>
+          <t>Software Engineer III - C# / Java</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
+          <t>https://www.indeed.com/viewjob?jk=fdaf569063c2010c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>Sperry Rail</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer Job</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Itron</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
+          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>University of California Berkeley</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>Itron</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Berxi</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior Data Engineer, Berxi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8891e7a3e0f8f62</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CURE Auto Insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,77 +1571,77 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,77 +1781,77 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,102 +1896,102 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Snowflake, Oracle, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff372041e842459</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,54 +2106,54 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2162,81 +2162,81 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,172 +2246,172 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
+          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Insights</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Guidewire Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Rockwoods Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,84 +2491,84 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2d40a87f71d317</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ISSM / Security Automation Engineer</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Snowflake, Oracle, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff372041e842459</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2582,11 +2582,11 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,15 +2613,15 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Terraform, Kubernetes, Git</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Developer Engineer in Testing</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Kafka</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d369a229cb2f75b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SHAKTECH CORP</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
+          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,102 +3016,102 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>ISSM / Security Automation Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
+          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Application Development Senior Advisor- Hybrid</t>
+          <t>Database Developer (PostgreSQL/Oracle)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, Jenkins, Maven, Jenkins, Git, Python, SQL</t>
+          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4000419aead97d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Frontapp</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,89 +3156,89 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3247,11 +3247,11 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f732389fad9f5f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; GitHub Platform Engineer (Hybrid)</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,542 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Sr Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Happen Bank</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee7752f8c95ab53</t>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>DevSecOps / Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>OpenShift Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Vital Services</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Allen, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Vital Services</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Oak Ridge, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Software Developer Engineer in Testing</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>The Clearing House Payments Company</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Kafka</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d369a229cb2f75b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Application Development Senior Advisor- Hybrid</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Bloomfield, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Scala, Kafka, Oracle, Jenkins, Maven, Jenkins, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4000419aead97d7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Database Architect</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SHAKTECH CORP</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Woodlawn, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Full Stack Solutions Developer – Java</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Full Stack Solutions Developer – Java</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Frontapp</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f732389fad9f5f1e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-20.xlsx
+++ b/results/job_matches_2026-08-20.xlsx
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0497d85a50331b</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ac15a01e20fc4f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Back-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ac15a01e20fc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf29ed5270e11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Back-End/Full-Stack Developer</t>
+          <t>Software Engineering - Senior Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf29ed5270e11</t>
+          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineering - Senior Engineer</t>
+          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
+          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
+          <t>Senior Production Operations Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
+          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
         </is>
       </c>
     </row>
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Production Operations Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor</t>
+          <t>Front-End/Full-Stack Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, IAM, Databricks, Hive</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab4f4baaddc2f11</t>
+          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
+          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Front-End/Full-Stack Developer</t>
+          <t>Snowflake_DBT Developers</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7737c23f8e09dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Snowflake_DBT Developers</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
+          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Engineer III - C# / Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,77 +1151,77 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=fdaf569063c2010c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - C# / Java</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sperry Rail</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdaf569063c2010c</t>
+          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sperry Rail</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
+          <t>https://www.indeed.com/viewjob?jk=08961c31c3764f09</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer Job</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0a4f0fdf890593</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Data Engineer Job</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Itron</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Berxi</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Itron</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Berxi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CURE Auto Insurance</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CURE Auto Insurance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,77 +1641,77 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Software Engineer II - ArcGIS Enterprise</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,42 +2246,42 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Java Software Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
+          <t>https://www.indeed.com/viewjob?jk=be57dd29022f1fe0</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer, Data, Senior (NE)</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Guidewire Data Architect</t>
+          <t>Engineer, Data, Senior (NE)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rockwoods Inc</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2d40a87f71d317</t>
+          <t>https://www.indeed.com/viewjob?jk=728ccd1f59eb0247</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Guidewire Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Rockwoods Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Snowflake, Oracle, MySQL, NoSQL, Data Modeling</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,19 +2526,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff372041e842459</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2d40a87f71d317</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Snowflake, Oracle, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216c50d086e32dde</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff372041e842459</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ISSM / Security Automation Engineer</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Database Developer (PostgreSQL/Oracle)</t>
+          <t>ISSM / Security Automation Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caee2aad6bb7dab7</t>
+          <t>https://www.indeed.com/viewjob?jk=854b2d4eca3cc1a0</t>
         </is>
       </c>
     </row>
@@ -3268,35 +3268,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>Spark, PySpark, Scala, NoSQL, ETL, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=dc92f44a3afb58a3</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DevSecOps / Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>DevSecOps / Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, GitHub Actions, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Developer Engineer in Testing</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d369a229cb2f75b9</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Application Development Senior Advisor- Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, Jenkins, Maven, Jenkins, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4000419aead97d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Senior Software Developer Engineer in Testing</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SHAKTECH CORP</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
+          <t>https://www.indeed.com/viewjob?jk=d369a229cb2f75b9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>SHAKTECH CORP</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
+          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ddda7a6ac90148d4</t>
         </is>
       </c>
     </row>
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,17 +3741,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Frontapp</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Frontapp</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f732389fad9f5f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>
       </c>
     </row>
